--- a/data/EntrevistasRealizadas.xlsx
+++ b/data/EntrevistasRealizadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Autónomo\EAS\web\generator\join tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C73C4A-5AF9-4C59-8365-FAFB6CD57422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2116AB2-0B6D-4271-B26F-263535C61626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Provincia" sheetId="3" r:id="rId3"/>
     <sheet name="Estudios" sheetId="4" r:id="rId4"/>
     <sheet name="Clase" sheetId="5" r:id="rId5"/>
-    <sheet name="EstimadorInterpretación" sheetId="7" r:id="rId6"/>
+    <sheet name="EstimadorInterpretación" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -3191,7 +3191,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68C715F5-DE9D-422F-932F-F51A089BBBE9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89B3375D-FFE2-415B-B6FF-FEF015E1A310}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11329,7 +11329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7165A089-7021-4D46-BA7D-06D816BB4728}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881971D6-7C81-448C-89AA-E45A0E459DC7}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>

--- a/data/EntrevistasRealizadas.xlsx
+++ b/data/EntrevistasRealizadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Autónomo\EAS\web\generator\join tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2116AB2-0B6D-4271-B26F-263535C61626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B4F56C-3222-4ADC-B70F-E4545DA2DC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2925,7 +2925,7 @@
     <t>62,11%</t>
   </si>
   <si>
-    <t>6.0</t>
+    <t>No ha trabajado</t>
   </si>
   <si>
     <t>9,54%</t>
@@ -3191,7 +3191,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89B3375D-FFE2-415B-B6FF-FEF015E1A310}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B897829-BA58-4226-8B64-C31BA25F5BEC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11329,7 +11329,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881971D6-7C81-448C-89AA-E45A0E459DC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22712AE4-6F69-4177-B982-EDF3748330CC}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>

--- a/data/EntrevistasRealizadas.xlsx
+++ b/data/EntrevistasRealizadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Autónomo\EAS\web\generator\join tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B4F56C-3222-4ADC-B70F-E4545DA2DC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDB603C-A9AF-476D-AAC3-82DA2F5F82D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,15 @@
     <sheet name="Provincia" sheetId="3" r:id="rId3"/>
     <sheet name="Estudios" sheetId="4" r:id="rId4"/>
     <sheet name="Clase" sheetId="5" r:id="rId5"/>
-    <sheet name="EstimadorInterpretación" sheetId="6" r:id="rId6"/>
+    <sheet name="Nacimiento" sheetId="6" r:id="rId6"/>
+    <sheet name="EstimadorInterpretación" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="1087">
   <si>
     <t>Tamaños muestrales en cada edición (entrevistas realizadas)*</t>
   </si>
@@ -3058,6 +3059,231 @@
   </si>
   <si>
     <t>53,95%</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>96,04%</t>
+  </si>
+  <si>
+    <t>94,95%</t>
+  </si>
+  <si>
+    <t>95,11%</t>
+  </si>
+  <si>
+    <t>92,68%</t>
+  </si>
+  <si>
+    <t>94,67%</t>
+  </si>
+  <si>
+    <t>95,71%</t>
+  </si>
+  <si>
+    <t>94,12%</t>
+  </si>
+  <si>
+    <t>93,65%</t>
+  </si>
+  <si>
+    <t>93,08%</t>
+  </si>
+  <si>
+    <t>94,0%</t>
+  </si>
+  <si>
+    <t>95,87%</t>
+  </si>
+  <si>
+    <t>94,53%</t>
+  </si>
+  <si>
+    <t>94,37%</t>
+  </si>
+  <si>
+    <t>92,93%</t>
+  </si>
+  <si>
+    <t>94,31%</t>
+  </si>
+  <si>
+    <t>24,72%</t>
+  </si>
+  <si>
+    <t>25,37%</t>
+  </si>
+  <si>
+    <t>21,93%</t>
+  </si>
+  <si>
+    <t>21,77%</t>
+  </si>
+  <si>
+    <t>34,68%</t>
+  </si>
+  <si>
+    <t>23,05%</t>
+  </si>
+  <si>
+    <t>23,23%</t>
+  </si>
+  <si>
+    <t>30,38%</t>
+  </si>
+  <si>
+    <t>49,45%</t>
+  </si>
+  <si>
+    <t>49,54%</t>
+  </si>
+  <si>
+    <t>49,56%</t>
+  </si>
+  <si>
+    <t>38,58%</t>
+  </si>
+  <si>
+    <t>46,19%</t>
+  </si>
+  <si>
+    <t>50,55%</t>
+  </si>
+  <si>
+    <t>50,46%</t>
+  </si>
+  <si>
+    <t>50,44%</t>
+  </si>
+  <si>
+    <t>61,42%</t>
+  </si>
+  <si>
+    <t>53,81%</t>
+  </si>
+  <si>
+    <t>Extrangero</t>
+  </si>
+  <si>
+    <t>3,96%</t>
+  </si>
+  <si>
+    <t>5,05%</t>
+  </si>
+  <si>
+    <t>4,89%</t>
+  </si>
+  <si>
+    <t>7,32%</t>
+  </si>
+  <si>
+    <t>5,33%</t>
+  </si>
+  <si>
+    <t>4,29%</t>
+  </si>
+  <si>
+    <t>5,88%</t>
+  </si>
+  <si>
+    <t>6,35%</t>
+  </si>
+  <si>
+    <t>6,0%</t>
+  </si>
+  <si>
+    <t>4,13%</t>
+  </si>
+  <si>
+    <t>5,47%</t>
+  </si>
+  <si>
+    <t>5,63%</t>
+  </si>
+  <si>
+    <t>7,07%</t>
+  </si>
+  <si>
+    <t>5,69%</t>
+  </si>
+  <si>
+    <t>22,77%</t>
+  </si>
+  <si>
+    <t>35,59%</t>
+  </si>
+  <si>
+    <t>15,38%</t>
+  </si>
+  <si>
+    <t>21,16%</t>
+  </si>
+  <si>
+    <t>40,35%</t>
+  </si>
+  <si>
+    <t>16,64%</t>
+  </si>
+  <si>
+    <t>47,39%</t>
+  </si>
+  <si>
+    <t>45,51%</t>
+  </si>
+  <si>
+    <t>42,7%</t>
+  </si>
+  <si>
+    <t>40,03%</t>
+  </si>
+  <si>
+    <t>43,08%</t>
+  </si>
+  <si>
+    <t>52,61%</t>
+  </si>
+  <si>
+    <t>54,49%</t>
+  </si>
+  <si>
+    <t>57,3%</t>
+  </si>
+  <si>
+    <t>59,97%</t>
+  </si>
+  <si>
+    <t>56,92%</t>
+  </si>
+  <si>
+    <t>24,81%</t>
+  </si>
+  <si>
+    <t>21,53%</t>
+  </si>
+  <si>
+    <t>35,02%</t>
+  </si>
+  <si>
+    <t>22,96%</t>
+  </si>
+  <si>
+    <t>23,0%</t>
+  </si>
+  <si>
+    <t>23,22%</t>
+  </si>
+  <si>
+    <t>49,18%</t>
+  </si>
+  <si>
+    <t>46,02%</t>
+  </si>
+  <si>
+    <t>50,82%</t>
+  </si>
+  <si>
+    <t>53,98%</t>
   </si>
   <si>
     <t>* Las casillas con valores enteros representan el número de entrevistas realizadas, es decir, personas que contestaron en cada edición; mientras que las casillas con porcentajes representan la distribución de las entrevistas realizadas en cada edición (% columna), en cada categoría de la variable de segmentación (% fila) o según sexo (% edición).</t>
@@ -3191,7 +3417,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B897829-BA58-4226-8B64-C31BA25F5BEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D82E85E0-3B13-4E8D-AB80-253FE746548A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5270,7 +5496,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>1011</v>
+        <v>1086</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -6505,7 +6731,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>1011</v>
+        <v>1086</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -8561,7 +8787,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>1011</v>
+        <v>1086</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -9591,7 +9817,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>1011</v>
+        <v>1086</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -11234,7 +11460,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>1011</v>
+        <v>1086</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -11329,7 +11555,825 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22712AE4-6F69-4177-B982-EDF3748330CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="17" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3079</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3047</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3072</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3127</v>
+      </c>
+      <c r="G4" s="1">
+        <v>12325</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3148</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3104</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3126</v>
+      </c>
+      <c r="K4" s="1">
+        <v>4978</v>
+      </c>
+      <c r="L4" s="1">
+        <v>14356</v>
+      </c>
+      <c r="M4" s="1">
+        <v>6227</v>
+      </c>
+      <c r="N4" s="1">
+        <v>6151</v>
+      </c>
+      <c r="O4" s="1">
+        <v>6198</v>
+      </c>
+      <c r="P4" s="1">
+        <v>8105</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>26681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1">
+        <v>127</v>
+      </c>
+      <c r="D8" s="1">
+        <v>162</v>
+      </c>
+      <c r="E8" s="1">
+        <v>158</v>
+      </c>
+      <c r="F8" s="1">
+        <v>247</v>
+      </c>
+      <c r="G8" s="1">
+        <v>694</v>
+      </c>
+      <c r="H8" s="1">
+        <v>141</v>
+      </c>
+      <c r="I8" s="1">
+        <v>194</v>
+      </c>
+      <c r="J8" s="1">
+        <v>212</v>
+      </c>
+      <c r="K8" s="1">
+        <v>370</v>
+      </c>
+      <c r="L8" s="1">
+        <v>917</v>
+      </c>
+      <c r="M8" s="1">
+        <v>268</v>
+      </c>
+      <c r="N8" s="1">
+        <v>356</v>
+      </c>
+      <c r="O8" s="1">
+        <v>370</v>
+      </c>
+      <c r="P8" s="1">
+        <v>617</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3206</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3209</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3230</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3374</v>
+      </c>
+      <c r="G12" s="1">
+        <v>13019</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3289</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3298</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3338</v>
+      </c>
+      <c r="K12" s="1">
+        <v>5348</v>
+      </c>
+      <c r="L12" s="1">
+        <v>15273</v>
+      </c>
+      <c r="M12" s="1">
+        <v>6495</v>
+      </c>
+      <c r="N12" s="1">
+        <v>6507</v>
+      </c>
+      <c r="O12" s="1">
+        <v>6568</v>
+      </c>
+      <c r="P12" s="1">
+        <v>8722</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>28292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="A17:M21"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC93B26F-3024-415E-8892-4F631E5AE680}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
